--- a/results/HR.xlsx
+++ b/results/HR.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aplikacije\sr-tokenizer-analysis\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3508AB-95BA-457E-875C-98D6C260048C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31480A37-5944-4B2E-AD2E-D5BD28B5E21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{AC18E37C-C5AB-4E14-A53E-0F1650FA5FDE}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{AC18E37C-C5AB-4E14-A53E-0F1650FA5FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="7">
   <si>
     <t>latinica+cirilica</t>
   </si>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>entropija</t>
+  </si>
+  <si>
+    <t>Redundancy</t>
+  </si>
+  <si>
+    <t>Entropy</t>
   </si>
 </sst>
 </file>
@@ -103,13 +109,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1051,6 +1057,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1683480128"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -2108,6 +2115,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1683474368"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -2203,63 +2211,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t>latinica (test 1 - no merge) </a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -2274,7 +2226,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>entropija</c:v>
+                  <c:v>Entropy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2653,7 +2605,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>redudantnost</c:v>
+                  <c:v>Redundancy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3049,7 +3001,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3108,7 +3060,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3150,7 +3102,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3181,6 +3133,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1683403328"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3209,7 +3162,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3360,7 +3313,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>entropija</c:v>
+                  <c:v>Entropy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3739,7 +3692,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>redudantnost</c:v>
+                  <c:v>Redundancy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4267,6 +4220,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1683471488"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -4446,7 +4400,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>entropija</c:v>
+                  <c:v>Entropy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4825,7 +4779,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>redudantnost</c:v>
+                  <c:v>Redundancy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5456,74 +5410,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>latinica + cirilica </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t>(test 1 - no merge) </a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -5538,7 +5425,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>entropija</c:v>
+                  <c:v>Entropy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5917,7 +5804,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>redudantnost</c:v>
+                  <c:v>Redundancy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6313,7 +6200,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -6372,7 +6259,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -6414,7 +6301,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -6474,7 +6361,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6521,7 +6408,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1200"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -9886,16 +9773,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>730250</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>565149</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>368299</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9958,16 +9845,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>517525</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9996,16 +9883,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>501649</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10716,15 +10603,15 @@
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B24">
@@ -10851,14 +10738,14 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E28" s="1"/>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
@@ -11440,78 +11327,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="E1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="1"/>
+      <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>261</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="1">
         <v>5.0885609964757403</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>0.34268776119378302</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="1">
         <v>4.9522150059318397</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="1">
         <v>0.35974131556508898</v>
       </c>
       <c r="G3">
         <v>261</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="1">
         <v>15.358982267659201</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="1">
         <v>0.25395532956556699</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="1">
         <v>15.5094961481238</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="1">
         <v>0.25396721342492601</v>
       </c>
     </row>
@@ -11519,31 +11406,31 @@
       <c r="A4">
         <v>271</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="1">
         <v>5.2215684818981796</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="1">
         <v>0.33119878191447</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <v>5.0630268148636004</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <v>0.35096887797325399</v>
       </c>
       <c r="G4">
         <v>311</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="1">
         <v>14.635775581703699</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="1">
         <v>0.26474280535892197</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="1">
         <v>14.909862247276401</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="1">
         <v>0.26102762403414298</v>
       </c>
     </row>
@@ -11551,31 +11438,31 @@
       <c r="A5">
         <v>281</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="1">
         <v>5.3566237851378302</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="1">
         <v>0.319393195107053</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>5.2420716579682702</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>0.33342477383605701</v>
       </c>
       <c r="G5">
         <v>361</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="1">
         <v>14.492649628803999</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="1">
         <v>0.26625760216264299</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="1">
         <v>14.8123512203472</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="1">
         <v>0.26164112704354497</v>
       </c>
     </row>
@@ -11583,31 +11470,31 @@
       <c r="A6">
         <v>291</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>5.4120350066910703</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>0.31758741005609997</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>5.31113543941147</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>0.329809325205496</v>
       </c>
       <c r="G6">
         <v>411</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="1">
         <v>14.346211191600499</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="1">
         <v>0.26927415679682498</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="1">
         <v>14.6293902522054</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="1">
         <v>0.26525381799606201</v>
       </c>
     </row>
@@ -11615,31 +11502,31 @@
       <c r="A7">
         <v>301</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="1">
         <v>5.43658358354583</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>0.31946449300372998</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>5.3350354322176399</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>0.331699896498796</v>
       </c>
       <c r="G7">
         <v>461</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="1">
         <v>14.345269437211201</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="1">
         <v>0.26927507649490501</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="1">
         <v>14.6306426663634</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="1">
         <v>0.26515795630296302</v>
       </c>
     </row>
@@ -11647,31 +11534,31 @@
       <c r="A8">
         <v>311</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>5.4442093227497503</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>0.32322941392832499</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>5.3476376613160399</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>0.334781496313247</v>
       </c>
       <c r="G8">
         <v>511</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="1">
         <v>14.349211422735801</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="1">
         <v>0.26906270375091401</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="1">
         <v>14.630365843620501</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="1">
         <v>0.26516391378899401</v>
       </c>
     </row>
@@ -11679,31 +11566,31 @@
       <c r="A9">
         <v>321</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="1">
         <v>5.4583881929384903</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="1">
         <v>0.32596115488060801</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="1">
         <v>5.3658677294740897</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>0.33695431161002298</v>
       </c>
       <c r="G9">
         <v>561</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="1">
         <v>14.3513442466444</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="1">
         <v>0.26894664922888301</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="1">
         <v>14.6548591402999</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="1">
         <v>0.26392838735719198</v>
       </c>
     </row>
@@ -11711,31 +11598,31 @@
       <c r="A10">
         <v>331</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="1">
         <v>5.47584779882951</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="1">
         <v>0.328095986472483</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="1">
         <v>5.3810130431679397</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
         <v>0.33931997111066198</v>
       </c>
       <c r="G10">
         <v>611</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="1">
         <v>14.3528081889398</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="1">
         <v>0.26886764253705397</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="1">
         <v>14.6669398895119</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="1">
         <v>0.26331819104918303</v>
       </c>
     </row>
@@ -11743,31 +11630,31 @@
       <c r="A11">
         <v>341</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>5.4932603930841504</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="1">
         <v>0.33006342667540001</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="1">
         <v>5.3991620049639</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>0.34114433156728902</v>
       </c>
       <c r="G11">
         <v>661</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="1">
         <v>14.3544095135333</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="1">
         <v>0.26878276151049402</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="1">
         <v>14.6680477150661</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="1">
         <v>0.26326005414483999</v>
       </c>
     </row>
@@ -11775,31 +11662,31 @@
       <c r="A12">
         <v>351</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="1">
         <v>5.5113228824436504</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="1">
         <v>0.33179300212561702</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="1">
         <v>5.4080517512069601</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>0.34393575071328403</v>
       </c>
       <c r="G12">
         <v>711</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="1">
         <v>14.364565858842701</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="1">
         <v>0.268255523993291</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="1">
         <v>14.6686402866065</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="1">
         <v>0.26322893532972502</v>
       </c>
     </row>
@@ -11807,31 +11694,31 @@
       <c r="A13">
         <v>361</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <v>5.5292287662631798</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <v>0.333395831629549</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
         <v>5.4225085459204196</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>0.34589912929729899</v>
       </c>
       <c r="G13">
         <v>761</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="1">
         <v>14.372726184048901</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="1">
         <v>0.26783498986294502</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="1">
         <v>14.670693133130801</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="1">
         <v>0.26312311440324898</v>
       </c>
     </row>
@@ -11839,31 +11726,31 @@
       <c r="A14">
         <v>371</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="1">
         <v>5.53922219891232</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="1">
         <v>0.335812730804943</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="1">
         <v>5.43436756459137</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1">
         <v>0.348036824510431</v>
       </c>
       <c r="G14">
         <v>811</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="1">
         <v>14.3841317016019</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="1">
         <v>0.26724780723934699</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="1">
         <v>14.672295544772499</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="1">
         <v>0.26303997124107198</v>
       </c>
     </row>
@@ -11871,31 +11758,31 @@
       <c r="A15">
         <v>381</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="1">
         <v>5.5437176920212599</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="1">
         <v>0.33875080768321097</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="1">
         <v>5.4415022249594598</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="1">
         <v>0.35060788681614702</v>
       </c>
       <c r="G15">
         <v>861</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="1">
         <v>14.3891936466121</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="1">
         <v>0.26698708859055498</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="1">
         <v>14.6739104082898</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="1">
         <v>0.26295669012147899</v>
       </c>
     </row>
@@ -11903,31 +11790,31 @@
       <c r="A16">
         <v>391</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="1">
         <v>5.5610352105054197</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="1">
         <v>0.34003554690087201</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="1">
         <v>5.4554103488046302</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
         <v>0.35224787504410199</v>
       </c>
       <c r="G16">
         <v>911</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="1">
         <v>14.3898791967175</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="1">
         <v>0.26694353389308301</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="1">
         <v>14.676502558574301</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="1">
         <v>0.26282334433464599</v>
       </c>
     </row>
@@ -11935,31 +11822,31 @@
       <c r="A17">
         <v>401</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>5.5635599431710299</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="1">
         <v>0.34264265124096299</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="1">
         <v>5.4596131582310496</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="1">
         <v>0.35492438877199101</v>
       </c>
       <c r="G17">
         <v>961</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="1">
         <v>14.414587282878401</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="1">
         <v>0.265680119260367</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="1">
         <v>14.680950326487901</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="1">
         <v>0.26259489240702</v>
       </c>
     </row>
@@ -11967,31 +11854,31 @@
       <c r="A18">
         <v>411</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>5.5641955366158102</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>0.34445094223699402</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>5.4601647248069396</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>0.35701140106074902</v>
       </c>
       <c r="G18">
         <v>1011</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="1">
         <v>14.4219057087011</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="1">
         <v>0.265300708378157</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="1">
         <v>14.6853059929918</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="1">
         <v>0.26236807629371101</v>
       </c>
     </row>
@@ -11999,31 +11886,31 @@
       <c r="A19">
         <v>421</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="1">
         <v>5.5655852601802804</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="1">
         <v>0.347335060977018</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="1">
         <v>5.4604458663269204</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="1">
         <v>0.35937042582923601</v>
       </c>
       <c r="G19">
         <v>1061</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="1">
         <v>14.422991457002199</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="1">
         <v>0.26524133579487302</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="1">
         <v>14.6875990528063</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="1">
         <v>0.262251702677406</v>
       </c>
     </row>
@@ -12031,31 +11918,31 @@
       <c r="A20">
         <v>431</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="1">
         <v>5.5657950813144401</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="1">
         <v>0.349960582105244</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="1">
         <v>5.46046837645798</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="1">
         <v>0.360827807815089</v>
       </c>
       <c r="G20">
         <v>1111</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="1">
         <v>14.4257182071372</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="1">
         <v>0.26509809691684399</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="1">
         <v>14.7108960048502</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="1">
         <v>0.26107710553554903</v>
       </c>
     </row>
@@ -12063,31 +11950,31 @@
       <c r="A21">
         <v>441</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="1">
         <v>5.5658641252611698</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="1">
         <v>0.35167286697016698</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="1">
         <v>5.4604928609601799</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="1">
         <v>0.36338814691037702</v>
       </c>
       <c r="G21">
         <v>1161</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="1">
         <v>14.4257099708309</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="1">
         <v>0.26509585262149099</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="1">
         <v>14.7142374837677</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="1">
         <v>0.26090795818687601</v>
       </c>
     </row>
@@ -12095,31 +11982,31 @@
       <c r="A22">
         <v>451</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="1">
         <v>5.5695540604907396</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="1">
         <v>0.35348326742596398</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="1">
         <v>5.4836752618056401</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="1">
         <v>0.363452123050714</v>
       </c>
       <c r="G22">
         <v>1211</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="1">
         <v>14.4270406265634</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="1">
         <v>0.26502646507345801</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="1">
         <v>14.73420671725</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="1">
         <v>0.25990022234862498</v>
       </c>
     </row>
@@ -12127,31 +12014,31 @@
       <c r="A23">
         <v>461</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="1">
         <v>5.5880593543514099</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="1">
         <v>0.35379170632887602</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="1">
         <v>5.4932650629885504</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="1">
         <v>0.36342124855446301</v>
       </c>
       <c r="G23">
         <v>1261</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="1">
         <v>14.439619925982299</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="1">
         <v>0.26438248978933099</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="1">
         <v>14.734589747424501</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="1">
         <v>0.25987934764001602</v>
       </c>
     </row>
@@ -12159,31 +12046,31 @@
       <c r="A24">
         <v>471</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="1">
         <v>5.6128703973313998</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="1">
         <v>0.35305461103370001</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="1">
         <v>5.4940869217794299</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="1">
         <v>0.36518567578469202</v>
       </c>
       <c r="G24">
         <v>1311</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="1">
         <v>14.441903083532299</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="1">
         <v>0.26426484211149698</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="1">
         <v>14.734859049323401</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="1">
         <v>0.25986456693621202</v>
       </c>
     </row>
@@ -12191,31 +12078,31 @@
       <c r="A25">
         <v>481</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="1">
         <v>5.6157888957874604</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="1">
         <v>0.35453964653325398</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="1">
         <v>5.4951553707247696</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="1">
         <v>0.366879662407673</v>
       </c>
       <c r="G25">
         <v>1361</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="1">
         <v>14.4429932271801</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="1">
         <v>0.264208038239508</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="1">
         <v>14.738033775762499</v>
       </c>
-      <c r="K25" s="3">
+      <c r="K25" s="1">
         <v>0.25970346410999201</v>
       </c>
     </row>
@@ -12223,31 +12110,31 @@
       <c r="A26">
         <v>491</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="1">
         <v>5.6262488269905999</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="1">
         <v>0.35562441287521201</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="1">
         <v>5.4999301877191904</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="1">
         <v>0.36810763799138202</v>
       </c>
       <c r="G26">
         <v>1411</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="1">
         <v>14.447409579093399</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="1">
         <v>0.26398064752105899</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="1">
         <v>14.738408602497699</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="1">
         <v>0.25968289171696501</v>
       </c>
     </row>
@@ -12255,31 +12142,31 @@
       <c r="A27">
         <v>501</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="1">
         <v>5.6323838022103203</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="1">
         <v>0.35641256397941601</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="1">
         <v>5.5005766793488897</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="1">
         <v>0.37001767318275097</v>
       </c>
       <c r="G27">
         <v>1461</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="1">
         <v>14.4570588918165</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="1">
         <v>0.26348586143881902</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="1">
         <v>14.738367125314699</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="1">
         <v>0.25968257605071798</v>
       </c>
     </row>
@@ -12287,31 +12174,31 @@
       <c r="A28">
         <v>511</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="1">
         <v>5.6433388728049998</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="1">
         <v>0.35662707087234202</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="1">
         <v>5.5060304949121202</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="1">
         <v>0.37156898945896599</v>
       </c>
       <c r="G28">
         <v>1511</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="1">
         <v>14.458063711735001</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="1">
         <v>0.26342799379772303</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="1">
         <v>14.748039984466301</v>
       </c>
-      <c r="K28" s="3">
+      <c r="K28" s="1">
         <v>0.259194683438077</v>
       </c>
     </row>
@@ -12319,31 +12206,31 @@
       <c r="A29">
         <v>521</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="1">
         <v>5.6660650251158202</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="1">
         <v>0.35572013977690398</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="1">
         <v>5.5100889815744498</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="1">
         <v>0.372524396980565</v>
       </c>
       <c r="G29">
         <v>1561</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="1">
         <v>14.4581121910641</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="1">
         <v>0.263419513743685</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="1">
         <v>14.7479762329277</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="1">
         <v>0.25919690356535402</v>
       </c>
     </row>
@@ -12351,31 +12238,31 @@
       <c r="A30">
         <v>531</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="1">
         <v>5.6696550963065198</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="1">
         <v>0.356962047502001</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="1">
         <v>5.5103998704218302</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="1">
         <v>0.37456953999515002</v>
       </c>
       <c r="G30">
         <v>1611</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="1">
         <v>14.4585996958723</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="1">
         <v>0.263392940911097</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="1">
         <v>14.7491197405781</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K30" s="1">
         <v>0.25913771797565299</v>
       </c>
     </row>
@@ -12383,31 +12270,31 @@
       <c r="A31">
         <v>541</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="1">
         <v>5.6855555289390001</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="1">
         <v>0.35631989984914902</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="1">
         <v>5.5139565935051502</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="1">
         <v>0.37619306832473298</v>
       </c>
       <c r="G31">
         <v>1661</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="1">
         <v>14.4597544257455</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="1">
         <v>0.26333090583955399</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="1">
         <v>14.7508451659283</v>
       </c>
-      <c r="K31" s="3">
+      <c r="K31" s="1">
         <v>0.25904924712312799</v>
       </c>
     </row>
@@ -12415,31 +12302,31 @@
       <c r="A32">
         <v>551</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="1">
         <v>5.6864420759397101</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>0.35736417810749099</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="1">
         <v>5.5145358297592697</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="1">
         <v>0.377885827331715</v>
       </c>
       <c r="G32">
         <v>1711</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="1">
         <v>14.459602872128899</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="1">
         <v>0.26333548727058198</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="1">
         <v>14.751024641496301</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="1">
         <v>0.25903924941397799</v>
       </c>
     </row>
@@ -12447,31 +12334,31 @@
       <c r="A33">
         <v>561</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="1">
         <v>5.6945171950401798</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="1">
         <v>0.35735680560955901</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="1">
         <v>5.5169340080940001</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="1">
         <v>0.37912193076425699</v>
       </c>
       <c r="G33">
         <v>1761</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="1">
         <v>14.4606278749574</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="1">
         <v>0.26327979294103498</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="1">
         <v>14.8161671831036</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="1">
         <v>0.25576481765044201</v>
       </c>
     </row>
@@ -12479,31 +12366,31 @@
       <c r="A34">
         <v>571</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="1">
         <v>5.6951755365757304</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="1">
         <v>0.35884223817989702</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="1">
         <v>5.5173568346737696</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="1">
         <v>0.380132637225087</v>
       </c>
       <c r="G34">
         <v>1811</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="1">
         <v>14.476244666238699</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="1">
         <v>0.26248129396671999</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="1">
         <v>14.8160056781166</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="1">
         <v>0.25577139513778802</v>
       </c>
     </row>
@@ -12511,31 +12398,31 @@
       <c r="A35">
         <v>581</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="1">
         <v>5.6956738511982197</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="1">
         <v>0.36009896855311402</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="1">
         <v>5.5207950793507203</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="1">
         <v>0.38099789934241002</v>
       </c>
       <c r="G35">
         <v>1861</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="1">
         <v>14.4782898107348</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="1">
         <v>0.26237495954686302</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="1">
         <v>14.8195259729459</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="1">
         <v>0.25559308513458501</v>
       </c>
     </row>
@@ -12543,31 +12430,31 @@
       <c r="A36">
         <v>591</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="1">
         <v>5.6962240373389301</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="1">
         <v>0.36154162829014203</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="1">
         <v>5.5250358879163999</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="1">
         <v>0.38216081342472302</v>
       </c>
       <c r="G36">
         <v>1911</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="1">
         <v>14.4791211206055</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="1">
         <v>0.26233126869874901</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="1">
         <v>14.8192215811187</v>
       </c>
-      <c r="K36" s="3">
+      <c r="K36" s="1">
         <v>0.255607223534279</v>
       </c>
     </row>
@@ -12575,31 +12462,31 @@
       <c r="A37">
         <v>601</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="1">
         <v>5.6968238524263999</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="1">
         <v>0.36253164877996202</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="1">
         <v>5.5256376496268302</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="1">
         <v>0.38349863187786498</v>
       </c>
       <c r="G37">
         <v>1961</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="1">
         <v>14.479987742356199</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="1">
         <v>0.26228283434785898</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="1">
         <v>14.8199209589564</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="1">
         <v>0.25557094094824301</v>
       </c>
     </row>
@@ -12607,31 +12494,31 @@
       <c r="A38">
         <v>611</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="1">
         <v>5.69720635889764</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="1">
         <v>0.363116412879464</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="1">
         <v>5.5261113827978301</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="1">
         <v>0.384433655863612</v>
       </c>
       <c r="G38">
         <v>2011</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="1">
         <v>14.4832027773517</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="1">
         <v>0.26211809973861</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J38" s="1">
         <v>14.8205792264372</v>
       </c>
-      <c r="K38" s="3">
+      <c r="K38" s="1">
         <v>0.255536997514481</v>
       </c>
     </row>
@@ -12639,31 +12526,31 @@
       <c r="A39">
         <v>621</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="1">
         <v>5.6977375199784204</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="1">
         <v>0.36450205145737902</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="1">
         <v>5.5295781729696802</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="1">
         <v>0.38579453611078901</v>
       </c>
       <c r="G39">
         <v>2061</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="1">
         <v>14.4854283463365</v>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="1">
         <v>0.26200156626390397</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="1">
         <v>14.8218683536155</v>
       </c>
-      <c r="K39" s="3">
+      <c r="K39" s="1">
         <v>0.255470432251383</v>
       </c>
     </row>
@@ -12671,31 +12558,31 @@
       <c r="A40">
         <v>631</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="1">
         <v>5.6984989418238499</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="1">
         <v>0.36543314359909201</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="1">
         <v>5.5296688738270801</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="1">
         <v>0.38673766842991902</v>
       </c>
       <c r="G40">
         <v>2111</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="1">
         <v>14.4877827394736</v>
       </c>
-      <c r="I40" s="3">
+      <c r="I40" s="1">
         <v>0.26188000843579101</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="1">
         <v>14.822033018576301</v>
       </c>
-      <c r="K40" s="3">
+      <c r="K40" s="1">
         <v>0.255461008832359</v>
       </c>
     </row>
@@ -12703,31 +12590,31 @@
       <c r="A41">
         <v>641</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="1">
         <v>5.7000813977346496</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="1">
         <v>0.36586034593882699</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="1">
         <v>5.5301108790195501</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="1">
         <v>0.38762986215901901</v>
       </c>
       <c r="G41">
         <v>2161</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="1">
         <v>14.489178291036801</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="1">
         <v>0.26180643034186502</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="1">
         <v>14.8244045083374</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="1">
         <v>0.25533947019311998</v>
       </c>
     </row>
@@ -12735,31 +12622,31 @@
       <c r="A42">
         <v>651</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="1">
         <v>5.7002089534420399</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="1">
         <v>0.36684148862769</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="1">
         <v>5.5304526875071298</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="1">
         <v>0.388705986429355</v>
       </c>
       <c r="G42">
         <v>2211</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="1">
         <v>14.489009331181499</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="1">
         <v>0.26181363209243902</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="1">
         <v>14.824569210098</v>
       </c>
-      <c r="K42" s="3">
+      <c r="K42" s="1">
         <v>0.25532998973042698</v>
       </c>
     </row>
@@ -12767,31 +12654,31 @@
       <c r="A43">
         <v>661</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="1">
         <v>5.7006204520863699</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="1">
         <v>0.36816802748225502</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="1">
         <v>5.5305467380633297</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="1">
         <v>0.38997437352763498</v>
       </c>
       <c r="G43">
         <v>2261</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="1">
         <v>14.4930614396756</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="1">
         <v>0.26159445511628598</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="1">
         <v>14.868662105955201</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="1">
         <v>0.253111971625814</v>
       </c>
     </row>
@@ -12799,31 +12686,31 @@
       <c r="A44">
         <v>671</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="1">
         <v>5.7014276660709298</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="1">
         <v>0.36923567156371601</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="1">
         <v>5.5324318691166896</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="1">
         <v>0.39102382428411497</v>
       </c>
       <c r="G44">
         <v>2311</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="1">
         <v>14.4930988481619</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="1">
         <v>0.261590538866807</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="1">
         <v>14.868556388569401</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="1">
         <v>0.25311546578004701</v>
       </c>
     </row>
@@ -12831,31 +12718,31 @@
       <c r="A45">
         <v>681</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="1">
         <v>5.7017001387817299</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="1">
         <v>0.370345411157111</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="1">
         <v>5.5325411352374196</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="1">
         <v>0.39172076585846699</v>
       </c>
       <c r="G45">
         <v>2361</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="1">
         <v>14.494496005715099</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="1">
         <v>0.26151788059477299</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="1">
         <v>14.8685181445796</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="1">
         <v>0.25311667134919402</v>
       </c>
     </row>
@@ -12863,31 +12750,31 @@
       <c r="A46">
         <v>691</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="1">
         <v>5.7039741349051898</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="1">
         <v>0.37103169136335901</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="1">
         <v>5.5326285471726502</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="1">
         <v>0.39310884158196602</v>
       </c>
       <c r="G46">
         <v>2411</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="1">
         <v>14.501755748357899</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="1">
         <v>0.26114699711600398</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="1">
         <v>14.8711664325011</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="1">
         <v>0.25298143907404502</v>
       </c>
     </row>
@@ -12895,31 +12782,31 @@
       <c r="A47">
         <v>701</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="1">
         <v>5.7041434362114298</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="1">
         <v>0.37193901903187299</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="1">
         <v>5.53279108457237</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="1">
         <v>0.39377996723402398</v>
       </c>
       <c r="G47">
         <v>2461</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="1">
         <v>14.501926045898999</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="1">
         <v>0.261137650019096</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="1">
         <v>14.871169397931499</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="1">
         <v>0.25298013398728098</v>
       </c>
     </row>
@@ -12927,31 +12814,31 @@
       <c r="A48">
         <v>711</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="1">
         <v>5.7050914154363204</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="1">
         <v>0.37311250512125199</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="1">
         <v>5.5328204801993799</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="1">
         <v>0.39428922121235399</v>
       </c>
       <c r="G48">
         <v>2511</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="1">
         <v>14.502083784816501</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="1">
         <v>0.261127668605805</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="1">
         <v>14.870985054378499</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="1">
         <v>0.25298845815250898</v>
       </c>
     </row>
@@ -12959,31 +12846,31 @@
       <c r="A49">
         <v>721</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="1">
         <v>5.7072851956522204</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="1">
         <v>0.374128514469316</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="1">
         <v>5.5328634870673303</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="1">
         <v>0.39546642369656299</v>
       </c>
       <c r="G49">
         <v>2561</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="1">
         <v>14.511294555593601</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I49" s="1">
         <v>0.260657580196202</v>
       </c>
-      <c r="J49" s="3">
+      <c r="J49" s="1">
         <v>14.8710471410594</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="1">
         <v>0.25298451353272</v>
       </c>
     </row>
@@ -12991,31 +12878,31 @@
       <c r="A50">
         <v>731</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="1">
         <v>5.7074110442109296</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="1">
         <v>0.37499995139756898</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="1">
         <v>5.5334538629539596</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="1">
         <v>0.39656498149290997</v>
       </c>
       <c r="G50">
         <v>2611</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="1">
         <v>14.5114167941512</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I50" s="1">
         <v>0.26064994297452199</v>
       </c>
-      <c r="J50" s="3">
+      <c r="J50" s="1">
         <v>14.8717172918037</v>
       </c>
-      <c r="K50" s="3">
+      <c r="K50" s="1">
         <v>0.25294991393163302</v>
       </c>
     </row>
@@ -13023,31 +12910,31 @@
       <c r="A51">
         <v>741</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="1">
         <v>5.7087656725628104</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="1">
         <v>0.37590053798878098</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="1">
         <v>5.5335917618144599</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="1">
         <v>0.39769460038916399</v>
       </c>
       <c r="G51">
         <v>2661</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="1">
         <v>14.5123368036401</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I51" s="1">
         <v>0.26060259912725697</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J51" s="1">
         <v>14.871734768291301</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K51" s="1">
         <v>0.252947329161264</v>
       </c>
     </row>
@@ -13055,49 +12942,49 @@
       <c r="A52">
         <v>751</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="1">
         <v>5.7089937232757899</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="1">
         <v>0.37691007528158499</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="1">
         <v>5.5339949348344204</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="1">
         <v>0.398777536931534</v>
       </c>
       <c r="G52">
         <v>2711</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="1">
         <v>14.5122316100089</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="1">
         <v>0.260606415100332</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="1">
         <v>14.8764280584335</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="1">
         <v>0.25271052434952102</v>
       </c>
     </row>
     <row r="53" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:51" x14ac:dyDescent="0.35">
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
     </row>
     <row r="57" spans="1:51" x14ac:dyDescent="0.35">
       <c r="B57">
